--- a/artfynd/A 5735-2024 artfynd.xlsx
+++ b/artfynd/A 5735-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,10 +821,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120407508</v>
+        <v>120407501</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,31 +837,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -869,10 +864,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528230</v>
+        <v>528437</v>
       </c>
       <c r="R3" t="n">
-        <v>7180042</v>
+        <v>7180020</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -904,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -914,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>gamla ringhack</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,6 +923,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -946,9 +942,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -966,10 +967,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120407501</v>
+        <v>120407544</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -982,21 +983,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1009,10 +1010,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528437</v>
+        <v>528244</v>
       </c>
       <c r="R4" t="n">
-        <v>7180020</v>
+        <v>7180026</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1044,7 +1045,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,12 +1055,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>på granlåga</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1074,27 +1070,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1112,10 +1088,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120407544</v>
+        <v>120407514</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1128,21 +1104,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1155,10 +1131,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528244</v>
+        <v>528639</v>
       </c>
       <c r="R5" t="n">
-        <v>7180026</v>
+        <v>7180387</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1190,7 +1166,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1200,7 +1176,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,7 +1196,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1233,10 +1234,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120407514</v>
+        <v>120407531</v>
       </c>
       <c r="B6" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,37 +1250,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528639</v>
+        <v>528412</v>
       </c>
       <c r="R6" t="n">
-        <v>7180387</v>
+        <v>7180115</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1311,7 +1309,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1321,12 +1319,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på död stående gran</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1335,34 +1328,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1379,10 +1346,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120407531</v>
+        <v>120407507</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1395,34 +1362,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528412</v>
+        <v>528230</v>
       </c>
       <c r="R7" t="n">
-        <v>7180115</v>
+        <v>7180117</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1454,7 +1429,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1464,7 +1439,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1475,6 +1455,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120407507</v>
+        <v>120407529</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1507,42 +1507,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528230</v>
+        <v>528606</v>
       </c>
       <c r="R8" t="n">
-        <v>7180117</v>
+        <v>7180320</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1574,7 +1566,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1584,12 +1576,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1600,26 +1587,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1636,10 +1603,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120407529</v>
+        <v>120407523</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1652,34 +1619,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528606</v>
+        <v>528293</v>
       </c>
       <c r="R9" t="n">
-        <v>7180320</v>
+        <v>7180322</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1711,7 +1681,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1721,7 +1691,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på mossig granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1730,8 +1705,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1748,10 +1749,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120407523</v>
+        <v>120407526</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1764,37 +1765,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528293</v>
+        <v>528541</v>
       </c>
       <c r="R10" t="n">
-        <v>7180322</v>
+        <v>7180241</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1826,7 +1824,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1836,12 +1834,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>på mossig granlåga</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,34 +1843,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1894,7 +1861,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120407526</v>
+        <v>120407545</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1928,16 +1895,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528541</v>
+        <v>528337</v>
       </c>
       <c r="R11" t="n">
-        <v>7180241</v>
+        <v>7180044</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1969,7 +1939,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1979,7 +1949,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1988,8 +1963,14 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2006,7 +1987,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120407545</v>
+        <v>120407543</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -2049,10 +2030,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528337</v>
+        <v>528219</v>
       </c>
       <c r="R12" t="n">
-        <v>7180044</v>
+        <v>7180072</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2084,7 +2065,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2094,12 +2075,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>riklig förekomst</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2132,7 +2108,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120407543</v>
+        <v>120407536</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -2175,10 +2151,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528219</v>
+        <v>528139</v>
       </c>
       <c r="R13" t="n">
-        <v>7180072</v>
+        <v>7180122</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2210,7 +2186,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2220,7 +2196,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2253,10 +2229,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120407536</v>
+        <v>120407503</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2269,26 +2245,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2296,10 +2277,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528139</v>
+        <v>528357</v>
       </c>
       <c r="R14" t="n">
-        <v>7180122</v>
+        <v>7180172</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2331,7 +2312,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2341,7 +2322,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2350,13 +2336,27 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2374,7 +2374,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120407503</v>
+        <v>120407504</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528357</v>
+        <v>528323</v>
       </c>
       <c r="R15" t="n">
-        <v>7180172</v>
+        <v>7180317</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2519,10 +2519,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120407504</v>
+        <v>120407546</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2535,31 +2535,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2567,10 +2562,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528323</v>
+        <v>528428</v>
       </c>
       <c r="R16" t="n">
-        <v>7180317</v>
+        <v>7180008</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2602,7 +2597,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2612,12 +2607,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2626,27 +2616,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2664,7 +2640,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120407546</v>
+        <v>120407539</v>
       </c>
       <c r="B17" t="n">
         <v>78542</v>
@@ -2707,10 +2683,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528428</v>
+        <v>528282</v>
       </c>
       <c r="R17" t="n">
-        <v>7180008</v>
+        <v>7180139</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2742,7 +2718,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2752,7 +2728,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2785,10 +2766,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120407539</v>
+        <v>120407506</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2801,26 +2782,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2828,10 +2814,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528282</v>
+        <v>528073</v>
       </c>
       <c r="R18" t="n">
-        <v>7180139</v>
+        <v>7180125</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2863,7 +2849,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2873,12 +2859,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2887,13 +2873,27 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120407506</v>
+        <v>120407530</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2927,42 +2927,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528073</v>
+        <v>528541</v>
       </c>
       <c r="R19" t="n">
-        <v>7180125</v>
+        <v>7180305</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2994,7 +2986,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3004,12 +2996,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3020,26 +3007,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3056,7 +3023,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120407530</v>
+        <v>120407528</v>
       </c>
       <c r="B20" t="n">
         <v>78542</v>
@@ -3096,10 +3063,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528541</v>
+        <v>528642</v>
       </c>
       <c r="R20" t="n">
-        <v>7180305</v>
+        <v>7180325</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3131,7 +3098,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3141,7 +3108,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3168,7 +3135,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120407528</v>
+        <v>120407537</v>
       </c>
       <c r="B21" t="n">
         <v>78542</v>
@@ -3208,10 +3175,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528642</v>
+        <v>528203</v>
       </c>
       <c r="R21" t="n">
-        <v>7180325</v>
+        <v>7180155</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3243,7 +3210,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3253,7 +3220,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3280,10 +3247,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120407537</v>
+        <v>120407515</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3296,34 +3263,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528203</v>
+        <v>528590</v>
       </c>
       <c r="R22" t="n">
-        <v>7180155</v>
+        <v>7180408</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3355,7 +3325,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3365,7 +3335,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>på stubbe av gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3374,8 +3349,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3392,10 +3393,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120407515</v>
+        <v>120407508</v>
       </c>
       <c r="B23" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3408,26 +3409,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3435,10 +3441,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528590</v>
+        <v>528230</v>
       </c>
       <c r="R23" t="n">
-        <v>7180408</v>
+        <v>7180042</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3470,7 +3476,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3480,12 +3486,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på stubbe av gran</t>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3494,7 +3500,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3513,14 +3518,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -6285,6 +6285,149 @@
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120407510</v>
+      </c>
+      <c r="B45" t="n">
+        <v>90934</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ytterrissjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>528398</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7180225</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>på granlåga upplyft av sina egna grova grenar</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5735-2024 artfynd.xlsx
+++ b/artfynd/A 5735-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120407511</v>
+        <v>120407505</v>
       </c>
       <c r="B2" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528545</v>
+        <v>528192</v>
       </c>
       <c r="R2" t="n">
-        <v>7180246</v>
+        <v>7180302</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på levande gran</t>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,14 +800,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -821,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120407501</v>
+        <v>120407521</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,21 +836,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -864,10 +863,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528437</v>
+        <v>528245</v>
       </c>
       <c r="R3" t="n">
-        <v>7180020</v>
+        <v>7180338</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -899,7 +898,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +908,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på granlåga och granstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -967,10 +966,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120407544</v>
+        <v>120407502</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -983,26 +982,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1010,10 +1014,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528244</v>
+        <v>528548</v>
       </c>
       <c r="R4" t="n">
-        <v>7180026</v>
+        <v>7180297</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1045,7 +1049,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1055,7 +1059,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,13 +1073,27 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1088,10 +1111,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120407514</v>
+        <v>120407547</v>
       </c>
       <c r="B5" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,21 +1127,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1131,10 +1154,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528639</v>
+        <v>528462</v>
       </c>
       <c r="R5" t="n">
-        <v>7180387</v>
+        <v>7180092</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1166,7 +1189,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1176,12 +1199,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på död stående gran</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1197,26 +1215,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1234,7 +1232,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120407531</v>
+        <v>120407530</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1274,10 +1272,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528412</v>
+        <v>528541</v>
       </c>
       <c r="R6" t="n">
-        <v>7180115</v>
+        <v>7180305</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1309,7 +1307,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1319,7 +1317,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1346,10 +1344,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120407507</v>
+        <v>120407545</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1362,31 +1360,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1394,10 +1387,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528230</v>
+        <v>528337</v>
       </c>
       <c r="R7" t="n">
-        <v>7180117</v>
+        <v>7180044</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1429,7 +1422,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1439,12 +1432,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>gamla ringhack</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1453,27 +1446,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1491,7 +1470,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120407529</v>
+        <v>120407527</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1531,7 +1510,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528606</v>
+        <v>528613</v>
       </c>
       <c r="R8" t="n">
         <v>7180320</v>
@@ -1566,7 +1545,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1576,7 +1555,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1603,10 +1582,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120407523</v>
+        <v>120407508</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1619,26 +1598,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1646,10 +1630,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528293</v>
+        <v>528230</v>
       </c>
       <c r="R9" t="n">
-        <v>7180322</v>
+        <v>7180042</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1681,7 +1665,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1691,12 +1675,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>på mossig granlåga</t>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1705,7 +1689,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1724,14 +1707,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1749,10 +1727,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120407526</v>
+        <v>120407522</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1765,34 +1743,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528541</v>
+        <v>528461</v>
       </c>
       <c r="R10" t="n">
-        <v>7180241</v>
+        <v>7180049</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1824,7 +1805,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1834,7 +1815,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1843,8 +1829,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1861,7 +1873,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120407545</v>
+        <v>120407532</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1895,19 +1907,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528337</v>
+        <v>528351</v>
       </c>
       <c r="R11" t="n">
-        <v>7180044</v>
+        <v>7180116</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1939,7 +1948,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1949,12 +1958,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>riklig förekomst</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1963,14 +1967,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1987,7 +1985,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120407543</v>
+        <v>120407536</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -2030,10 +2028,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528219</v>
+        <v>528139</v>
       </c>
       <c r="R12" t="n">
-        <v>7180072</v>
+        <v>7180122</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2065,7 +2063,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2075,7 +2073,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2108,7 +2106,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120407536</v>
+        <v>120407529</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -2142,19 +2140,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528139</v>
+        <v>528606</v>
       </c>
       <c r="R13" t="n">
-        <v>7180122</v>
+        <v>7180320</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2186,7 +2181,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2196,7 +2191,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2205,14 +2200,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2229,10 +2218,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120407503</v>
+        <v>120407544</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2245,31 +2234,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2277,10 +2261,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528357</v>
+        <v>528244</v>
       </c>
       <c r="R14" t="n">
-        <v>7180172</v>
+        <v>7180026</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2312,7 +2296,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2322,12 +2306,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2336,27 +2315,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2374,10 +2339,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120407504</v>
+        <v>120407512</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2390,31 +2355,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2422,10 +2382,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528323</v>
+        <v>528652</v>
       </c>
       <c r="R15" t="n">
-        <v>7180317</v>
+        <v>7180371</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2457,7 +2417,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2467,12 +2427,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>gamla ringhack</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2481,6 +2441,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2499,9 +2460,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2519,7 +2485,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120407546</v>
+        <v>120407531</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2553,19 +2519,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528428</v>
+        <v>528412</v>
       </c>
       <c r="R16" t="n">
-        <v>7180008</v>
+        <v>7180115</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2597,7 +2560,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2607,7 +2570,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2616,14 +2579,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2640,10 +2597,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120407539</v>
+        <v>120407500</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2656,21 +2613,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2683,10 +2640,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528282</v>
+        <v>528382</v>
       </c>
       <c r="R17" t="n">
-        <v>7180139</v>
+        <v>7180168</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2718,7 +2675,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2728,12 +2685,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på rotvälta gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2749,6 +2706,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2766,10 +2743,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120407506</v>
+        <v>120407516</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2782,42 +2759,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528073</v>
+        <v>528460</v>
       </c>
       <c r="R18" t="n">
-        <v>7180125</v>
+        <v>7180155</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2849,7 +2818,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2859,12 +2828,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>gamla ringhack</t>
+          <t>på levande gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2875,26 +2844,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2911,7 +2860,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120407530</v>
+        <v>120407535</v>
       </c>
       <c r="B19" t="n">
         <v>78542</v>
@@ -2945,16 +2894,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528541</v>
+        <v>528075</v>
       </c>
       <c r="R19" t="n">
-        <v>7180305</v>
+        <v>7180118</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2986,7 +2938,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2996,7 +2948,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3005,8 +2957,14 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3023,10 +2981,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120407528</v>
+        <v>120407501</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3039,34 +2997,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528642</v>
+        <v>528437</v>
       </c>
       <c r="R20" t="n">
-        <v>7180325</v>
+        <v>7180020</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3098,7 +3059,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3108,7 +3069,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3117,8 +3083,34 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3135,10 +3127,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120407537</v>
+        <v>120407509</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3151,34 +3143,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528203</v>
+        <v>528353</v>
       </c>
       <c r="R21" t="n">
-        <v>7180155</v>
+        <v>7180029</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3220,7 +3220,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>gamla ringhack svåra att se på bild</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3231,6 +3236,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3247,7 +3272,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120407515</v>
+        <v>120407518</v>
       </c>
       <c r="B22" t="n">
         <v>90576</v>
@@ -3290,10 +3315,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528590</v>
+        <v>528380</v>
       </c>
       <c r="R22" t="n">
-        <v>7180408</v>
+        <v>7180165</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3325,7 +3350,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3335,12 +3360,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>på stubbe av gran</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3370,12 +3395,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3393,10 +3418,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120407508</v>
+        <v>120407517</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3409,42 +3434,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528230</v>
+        <v>528388</v>
       </c>
       <c r="R23" t="n">
-        <v>7180042</v>
+        <v>7180174</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3476,7 +3493,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3486,12 +3503,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>gamla ringhack</t>
+          <t>på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3502,26 +3519,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3538,10 +3535,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120407522</v>
+        <v>120407504</v>
       </c>
       <c r="B24" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3554,26 +3551,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3581,10 +3583,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528461</v>
+        <v>528323</v>
       </c>
       <c r="R24" t="n">
-        <v>7180049</v>
+        <v>7180317</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3616,7 +3618,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3626,12 +3628,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på granstubbe</t>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3640,7 +3642,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3659,14 +3660,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3684,7 +3680,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120407540</v>
+        <v>120407528</v>
       </c>
       <c r="B25" t="n">
         <v>78542</v>
@@ -3718,19 +3714,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528288</v>
+        <v>528642</v>
       </c>
       <c r="R25" t="n">
-        <v>7180107</v>
+        <v>7180325</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3762,7 +3755,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3772,7 +3765,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3781,14 +3774,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3805,10 +3792,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120407521</v>
+        <v>120407534</v>
       </c>
       <c r="B26" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3821,21 +3808,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3848,10 +3835,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528245</v>
+        <v>528126</v>
       </c>
       <c r="R26" t="n">
-        <v>7180338</v>
+        <v>7180169</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3883,7 +3870,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3893,12 +3880,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>på granlåga och granstubbe</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3913,27 +3895,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3951,7 +3913,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120407535</v>
+        <v>120407540</v>
       </c>
       <c r="B27" t="n">
         <v>78542</v>
@@ -3994,10 +3956,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528075</v>
+        <v>528288</v>
       </c>
       <c r="R27" t="n">
-        <v>7180118</v>
+        <v>7180107</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -4029,7 +3991,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4039,7 +4001,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4072,10 +4034,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120407525</v>
+        <v>120407520</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4088,34 +4050,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528528</v>
+        <v>528255</v>
       </c>
       <c r="R28" t="n">
-        <v>7180138</v>
+        <v>7180313</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4147,7 +4112,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4157,7 +4122,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>på stående död gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4166,8 +4136,34 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4184,10 +4180,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120407517</v>
+        <v>120407546</v>
       </c>
       <c r="B29" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4200,34 +4196,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528388</v>
+        <v>528428</v>
       </c>
       <c r="R29" t="n">
-        <v>7180174</v>
+        <v>7180008</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4259,7 +4258,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4269,12 +4268,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>på högstubbe av gran</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4283,8 +4277,14 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4301,7 +4301,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120407519</v>
+        <v>120407511</v>
       </c>
       <c r="B30" t="n">
         <v>90576</v>
@@ -4335,16 +4335,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528442</v>
+        <v>528545</v>
       </c>
       <c r="R30" t="n">
-        <v>7180203</v>
+        <v>7180246</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4376,7 +4379,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4386,12 +4389,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>på granstubbe</t>
+          <t>på levande gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4400,8 +4403,34 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4418,10 +4447,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120407505</v>
+        <v>120407519</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4434,42 +4463,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528192</v>
+        <v>528442</v>
       </c>
       <c r="R31" t="n">
-        <v>7180302</v>
+        <v>7180203</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4501,7 +4522,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4511,12 +4532,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>gamla ringhack</t>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4527,26 +4548,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4563,7 +4564,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120407509</v>
+        <v>120407506</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -4611,10 +4612,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528353</v>
+        <v>528073</v>
       </c>
       <c r="R32" t="n">
-        <v>7180029</v>
+        <v>7180125</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4646,7 +4647,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4656,12 +4657,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>gamla ringhack svåra att se på bild</t>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4708,10 +4709,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120407500</v>
+        <v>120407539</v>
       </c>
       <c r="B33" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4724,21 +4725,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4751,10 +4752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528382</v>
+        <v>528282</v>
       </c>
       <c r="R33" t="n">
-        <v>7180168</v>
+        <v>7180139</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4786,7 +4787,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4796,12 +4797,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>på rotvälta gran</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4817,26 +4818,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5000,7 +4981,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120407534</v>
+        <v>120407541</v>
       </c>
       <c r="B35" t="n">
         <v>78542</v>
@@ -5043,10 +5024,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528126</v>
+        <v>528291</v>
       </c>
       <c r="R35" t="n">
-        <v>7180169</v>
+        <v>7180101</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -5078,7 +5059,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5088,7 +5069,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5103,7 +5084,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5121,10 +5102,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120407547</v>
+        <v>120407507</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5137,26 +5118,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5164,10 +5150,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528462</v>
+        <v>528230</v>
       </c>
       <c r="R36" t="n">
-        <v>7180092</v>
+        <v>7180117</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5199,7 +5185,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5209,7 +5195,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5218,13 +5209,27 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5242,10 +5247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120407541</v>
+        <v>120407503</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5258,26 +5263,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5285,10 +5295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528291</v>
+        <v>528357</v>
       </c>
       <c r="R37" t="n">
-        <v>7180101</v>
+        <v>7180172</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5320,7 +5330,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5330,7 +5340,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5339,13 +5354,27 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5363,10 +5392,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120407502</v>
+        <v>120407525</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5379,42 +5408,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528548</v>
+        <v>528528</v>
       </c>
       <c r="R38" t="n">
-        <v>7180297</v>
+        <v>7180138</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5446,7 +5467,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5456,12 +5477,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5472,26 +5488,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5508,10 +5504,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120407520</v>
+        <v>120407523</v>
       </c>
       <c r="B39" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5524,21 +5520,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5551,10 +5547,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528255</v>
+        <v>528293</v>
       </c>
       <c r="R39" t="n">
-        <v>7180313</v>
+        <v>7180322</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5586,7 +5582,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5596,12 +5592,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>på stående död gran</t>
+          <t>på mossig granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5631,12 +5627,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5654,7 +5650,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120407518</v>
+        <v>120407514</v>
       </c>
       <c r="B40" t="n">
         <v>90576</v>
@@ -5697,10 +5693,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528380</v>
+        <v>528639</v>
       </c>
       <c r="R40" t="n">
-        <v>7180165</v>
+        <v>7180387</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5732,7 +5728,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5742,7 +5738,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5800,7 +5796,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120407516</v>
+        <v>120407515</v>
       </c>
       <c r="B41" t="n">
         <v>90576</v>
@@ -5834,16 +5830,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528460</v>
+        <v>528590</v>
       </c>
       <c r="R41" t="n">
-        <v>7180155</v>
+        <v>7180408</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5875,7 +5874,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5885,12 +5884,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>på levande gran</t>
+          <t>på stubbe av gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5899,8 +5898,34 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5917,7 +5942,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120407532</v>
+        <v>120407537</v>
       </c>
       <c r="B42" t="n">
         <v>78542</v>
@@ -5957,10 +5982,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528351</v>
+        <v>528203</v>
       </c>
       <c r="R42" t="n">
-        <v>7180116</v>
+        <v>7180155</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5992,7 +6017,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6002,7 +6027,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6029,7 +6054,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120407527</v>
+        <v>120407526</v>
       </c>
       <c r="B43" t="n">
         <v>78542</v>
@@ -6069,10 +6094,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528613</v>
+        <v>528541</v>
       </c>
       <c r="R43" t="n">
-        <v>7180320</v>
+        <v>7180241</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -6104,7 +6129,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6114,7 +6139,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6141,10 +6166,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120407512</v>
+        <v>120407543</v>
       </c>
       <c r="B44" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6157,21 +6182,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6184,10 +6209,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528652</v>
+        <v>528219</v>
       </c>
       <c r="R44" t="n">
-        <v>7180371</v>
+        <v>7180072</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -6219,7 +6244,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6229,12 +6254,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>på död stående gran</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6249,27 +6269,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 5735-2024 artfynd.xlsx
+++ b/artfynd/A 5735-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120407505</v>
+        <v>120407540</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528192</v>
+        <v>528288</v>
       </c>
       <c r="R2" t="n">
-        <v>7180302</v>
+        <v>7180107</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -758,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,27 +772,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -820,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120407521</v>
+        <v>120407532</v>
       </c>
       <c r="B3" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,37 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528245</v>
+        <v>528351</v>
       </c>
       <c r="R3" t="n">
-        <v>7180338</v>
+        <v>7180116</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -898,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -908,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på granlåga och granstubbe</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,34 +890,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -966,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120407502</v>
+        <v>120407521</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -982,31 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1014,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528548</v>
+        <v>528245</v>
       </c>
       <c r="R4" t="n">
-        <v>7180297</v>
+        <v>7180338</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1049,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1059,12 +996,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>gamla ringhack</t>
+          <t>på granlåga och granstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,6 +1010,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1091,9 +1029,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1111,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120407547</v>
+        <v>120407508</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1127,26 +1070,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1154,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528462</v>
+        <v>528230</v>
       </c>
       <c r="R5" t="n">
-        <v>7180092</v>
+        <v>7180042</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1189,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1199,7 +1147,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1208,13 +1161,27 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1232,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120407530</v>
+        <v>120407516</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1248,21 +1215,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1272,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528541</v>
+        <v>528460</v>
       </c>
       <c r="R6" t="n">
-        <v>7180305</v>
+        <v>7180155</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1307,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1317,7 +1284,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på levande gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1344,10 +1316,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120407545</v>
+        <v>120407501</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1360,21 +1332,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1387,10 +1359,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528337</v>
+        <v>528437</v>
       </c>
       <c r="R7" t="n">
-        <v>7180044</v>
+        <v>7180020</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1422,7 +1394,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1432,12 +1404,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1452,7 +1424,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1470,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120407527</v>
+        <v>120407523</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1486,34 +1478,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528613</v>
+        <v>528293</v>
       </c>
       <c r="R8" t="n">
-        <v>7180320</v>
+        <v>7180322</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1545,7 +1540,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1555,7 +1550,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på mossig granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1564,8 +1564,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1582,10 +1608,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120407508</v>
+        <v>120407537</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1598,42 +1624,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528230</v>
+        <v>528203</v>
       </c>
       <c r="R9" t="n">
-        <v>7180042</v>
+        <v>7180155</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1665,7 +1683,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1675,12 +1693,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1691,26 +1704,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1727,10 +1720,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120407522</v>
+        <v>120407543</v>
       </c>
       <c r="B10" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1743,21 +1736,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1770,10 +1763,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528461</v>
+        <v>528219</v>
       </c>
       <c r="R10" t="n">
-        <v>7180049</v>
+        <v>7180072</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1805,7 +1798,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1815,12 +1808,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>på granstubbe</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1835,27 +1823,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1873,7 +1841,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120407532</v>
+        <v>120407539</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1907,16 +1875,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528351</v>
+        <v>528282</v>
       </c>
       <c r="R11" t="n">
-        <v>7180116</v>
+        <v>7180139</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1948,7 +1919,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1958,7 +1929,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1967,8 +1943,14 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1985,10 +1967,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120407536</v>
+        <v>120407522</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2001,21 +1983,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2028,10 +2010,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528139</v>
+        <v>528461</v>
       </c>
       <c r="R12" t="n">
-        <v>7180122</v>
+        <v>7180049</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2063,7 +2045,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2073,7 +2055,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2088,7 +2075,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2106,10 +2113,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120407529</v>
+        <v>120407503</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2122,34 +2129,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528606</v>
+        <v>528357</v>
       </c>
       <c r="R13" t="n">
-        <v>7180320</v>
+        <v>7180172</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2181,7 +2196,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2191,7 +2206,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2202,6 +2222,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2218,10 +2258,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120407544</v>
+        <v>120407512</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2234,21 +2274,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2261,10 +2301,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528244</v>
+        <v>528652</v>
       </c>
       <c r="R14" t="n">
-        <v>7180026</v>
+        <v>7180371</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2296,7 +2336,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2306,7 +2346,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2321,7 +2366,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2339,10 +2404,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120407512</v>
+        <v>120407534</v>
       </c>
       <c r="B15" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2355,21 +2420,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2382,10 +2447,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528652</v>
+        <v>528126</v>
       </c>
       <c r="R15" t="n">
-        <v>7180371</v>
+        <v>7180169</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2417,7 +2482,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2427,12 +2492,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>på död stående gran</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2447,27 +2507,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2485,7 +2525,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120407531</v>
+        <v>120407545</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2519,16 +2559,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528412</v>
+        <v>528337</v>
       </c>
       <c r="R16" t="n">
-        <v>7180115</v>
+        <v>7180044</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2560,7 +2603,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2570,7 +2613,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,8 +2627,14 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2597,10 +2651,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120407500</v>
+        <v>120407536</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2613,21 +2667,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2640,10 +2694,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528382</v>
+        <v>528139</v>
       </c>
       <c r="R17" t="n">
-        <v>7180168</v>
+        <v>7180122</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2675,7 +2729,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2685,12 +2739,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>på rotvälta gran</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2705,27 +2754,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2743,10 +2772,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120407516</v>
+        <v>120407504</v>
       </c>
       <c r="B18" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2759,34 +2788,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528460</v>
+        <v>528323</v>
       </c>
       <c r="R18" t="n">
-        <v>7180155</v>
+        <v>7180317</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2818,7 +2855,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2828,12 +2865,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på levande gran</t>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2844,6 +2881,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2860,10 +2917,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120407535</v>
+        <v>120407505</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2876,26 +2933,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2903,10 +2965,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528075</v>
+        <v>528192</v>
       </c>
       <c r="R19" t="n">
-        <v>7180118</v>
+        <v>7180302</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2938,7 +3000,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2948,7 +3010,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2957,13 +3024,27 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2981,10 +3062,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120407501</v>
+        <v>120407530</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2997,37 +3078,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528437</v>
+        <v>528541</v>
       </c>
       <c r="R20" t="n">
-        <v>7180020</v>
+        <v>7180305</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3059,7 +3137,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3069,12 +3147,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>på granlåga</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3083,34 +3156,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3127,10 +3174,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120407509</v>
+        <v>120407541</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3143,31 +3190,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3175,10 +3217,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528353</v>
+        <v>528291</v>
       </c>
       <c r="R21" t="n">
-        <v>7180029</v>
+        <v>7180101</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3210,7 +3252,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3220,12 +3262,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>gamla ringhack svåra att se på bild</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3234,27 +3271,13 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3272,10 +3295,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120407518</v>
+        <v>120407529</v>
       </c>
       <c r="B22" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3288,37 +3311,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528380</v>
+        <v>528606</v>
       </c>
       <c r="R22" t="n">
-        <v>7180165</v>
+        <v>7180320</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3350,7 +3370,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3360,12 +3380,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>på död stående gran</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3374,34 +3389,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3418,10 +3407,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120407517</v>
+        <v>120407527</v>
       </c>
       <c r="B23" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3434,21 +3423,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3458,10 +3447,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528388</v>
+        <v>528613</v>
       </c>
       <c r="R23" t="n">
-        <v>7180174</v>
+        <v>7180320</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3493,7 +3482,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3503,12 +3492,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>på högstubbe av gran</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3535,10 +3519,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120407504</v>
+        <v>120407514</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3551,31 +3535,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3583,10 +3562,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528323</v>
+        <v>528639</v>
       </c>
       <c r="R24" t="n">
-        <v>7180317</v>
+        <v>7180387</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3618,7 +3597,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3628,12 +3607,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>gamla ringhack</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3642,6 +3621,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3660,9 +3640,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3680,7 +3665,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120407528</v>
+        <v>120407544</v>
       </c>
       <c r="B25" t="n">
         <v>78542</v>
@@ -3714,16 +3699,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528642</v>
+        <v>528244</v>
       </c>
       <c r="R25" t="n">
-        <v>7180325</v>
+        <v>7180026</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3755,7 +3743,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3765,7 +3753,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3774,8 +3762,14 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3792,7 +3786,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120407534</v>
+        <v>120407531</v>
       </c>
       <c r="B26" t="n">
         <v>78542</v>
@@ -3826,19 +3820,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528126</v>
+        <v>528412</v>
       </c>
       <c r="R26" t="n">
-        <v>7180169</v>
+        <v>7180115</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3870,7 +3861,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3880,7 +3871,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3889,14 +3880,8 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3913,10 +3898,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120407540</v>
+        <v>120407515</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3929,21 +3914,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3956,10 +3941,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528288</v>
+        <v>528590</v>
       </c>
       <c r="R27" t="n">
-        <v>7180107</v>
+        <v>7180408</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3991,7 +3976,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4001,7 +3986,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>på stubbe av gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4017,6 +4007,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4034,7 +4044,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120407520</v>
+        <v>120407511</v>
       </c>
       <c r="B28" t="n">
         <v>90576</v>
@@ -4077,10 +4087,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528255</v>
+        <v>528545</v>
       </c>
       <c r="R28" t="n">
-        <v>7180313</v>
+        <v>7180246</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4112,7 +4122,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4122,12 +4132,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>på stående död gran</t>
+          <t>på levande gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4157,12 +4167,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4180,10 +4190,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120407546</v>
+        <v>120407509</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4196,26 +4206,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4223,10 +4238,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528428</v>
+        <v>528353</v>
       </c>
       <c r="R29" t="n">
-        <v>7180008</v>
+        <v>7180029</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4258,7 +4273,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4268,7 +4283,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>gamla ringhack svåra att se på bild</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4277,13 +4297,27 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4301,10 +4335,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120407511</v>
+        <v>120407525</v>
       </c>
       <c r="B30" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4317,37 +4351,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528545</v>
+        <v>528528</v>
       </c>
       <c r="R30" t="n">
-        <v>7180246</v>
+        <v>7180138</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4379,7 +4410,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4389,12 +4420,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>på levande gran</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4403,34 +4429,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4447,10 +4447,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120407519</v>
+        <v>120407506</v>
       </c>
       <c r="B31" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4463,34 +4463,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528442</v>
+        <v>528073</v>
       </c>
       <c r="R31" t="n">
-        <v>7180203</v>
+        <v>7180125</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4522,7 +4530,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4532,12 +4540,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>på granstubbe</t>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4548,6 +4556,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4564,10 +4592,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120407506</v>
+        <v>120407526</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4580,42 +4608,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528073</v>
+        <v>528541</v>
       </c>
       <c r="R32" t="n">
-        <v>7180125</v>
+        <v>7180241</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4647,7 +4667,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4657,12 +4677,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4673,26 +4688,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4709,10 +4704,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120407539</v>
+        <v>120407502</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4725,26 +4720,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528282</v>
+        <v>528548</v>
       </c>
       <c r="R33" t="n">
-        <v>7180139</v>
+        <v>7180297</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4811,13 +4811,27 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4835,10 +4849,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120407524</v>
+        <v>120407520</v>
       </c>
       <c r="B34" t="n">
-        <v>90598</v>
+        <v>90576</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4851,21 +4865,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4878,10 +4892,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528083</v>
+        <v>528255</v>
       </c>
       <c r="R34" t="n">
-        <v>7180143</v>
+        <v>7180313</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4913,7 +4927,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4923,12 +4937,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>på granlåga med bark</t>
+          <t>på stående död gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4958,12 +4972,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4981,7 +4995,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120407541</v>
+        <v>120407546</v>
       </c>
       <c r="B35" t="n">
         <v>78542</v>
@@ -5024,10 +5038,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528291</v>
+        <v>528428</v>
       </c>
       <c r="R35" t="n">
-        <v>7180101</v>
+        <v>7180008</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -5059,7 +5073,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5069,7 +5083,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5102,10 +5116,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120407507</v>
+        <v>120407528</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5118,42 +5132,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528230</v>
+        <v>528642</v>
       </c>
       <c r="R36" t="n">
-        <v>7180117</v>
+        <v>7180325</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5185,7 +5191,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5195,12 +5201,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5211,26 +5212,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5247,10 +5228,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120407503</v>
+        <v>120407535</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5263,31 +5244,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5295,10 +5271,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528357</v>
+        <v>528075</v>
       </c>
       <c r="R37" t="n">
-        <v>7180172</v>
+        <v>7180118</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5330,7 +5306,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5340,12 +5316,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5354,27 +5325,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5392,7 +5349,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120407525</v>
+        <v>120407547</v>
       </c>
       <c r="B38" t="n">
         <v>78542</v>
@@ -5426,16 +5383,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528528</v>
+        <v>528462</v>
       </c>
       <c r="R38" t="n">
-        <v>7180138</v>
+        <v>7180092</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5467,7 +5427,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5477,7 +5437,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5486,8 +5446,14 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5504,10 +5470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120407523</v>
+        <v>120407518</v>
       </c>
       <c r="B39" t="n">
-        <v>90598</v>
+        <v>90576</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5520,21 +5486,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5547,10 +5513,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528293</v>
+        <v>528380</v>
       </c>
       <c r="R39" t="n">
-        <v>7180322</v>
+        <v>7180165</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5582,7 +5548,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5592,12 +5558,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>på mossig granlåga</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5627,12 +5593,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5650,10 +5616,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120407514</v>
+        <v>120407524</v>
       </c>
       <c r="B40" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5666,21 +5632,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5693,10 +5659,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528639</v>
+        <v>528083</v>
       </c>
       <c r="R40" t="n">
-        <v>7180387</v>
+        <v>7180143</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5728,7 +5694,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5738,12 +5704,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>på granlåga med bark</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5773,12 +5739,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5796,7 +5762,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120407515</v>
+        <v>120407519</v>
       </c>
       <c r="B41" t="n">
         <v>90576</v>
@@ -5830,19 +5796,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528590</v>
+        <v>528442</v>
       </c>
       <c r="R41" t="n">
-        <v>7180408</v>
+        <v>7180203</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5874,7 +5837,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5884,12 +5847,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>på stubbe av gran</t>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5898,34 +5861,8 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5942,10 +5879,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120407537</v>
+        <v>120407507</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5958,34 +5895,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528203</v>
+        <v>528230</v>
       </c>
       <c r="R42" t="n">
-        <v>7180155</v>
+        <v>7180117</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -6017,7 +5962,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6027,7 +5972,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6038,6 +5988,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -6054,10 +6024,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120407526</v>
+        <v>120407500</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6070,34 +6040,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528541</v>
+        <v>528382</v>
       </c>
       <c r="R43" t="n">
-        <v>7180241</v>
+        <v>7180168</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -6129,7 +6102,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6139,7 +6112,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>på rotvälta gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6148,8 +6126,34 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6166,10 +6170,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120407543</v>
+        <v>120407517</v>
       </c>
       <c r="B44" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6182,37 +6186,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528219</v>
+        <v>528388</v>
       </c>
       <c r="R44" t="n">
-        <v>7180072</v>
+        <v>7180174</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -6244,7 +6245,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6254,7 +6255,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6263,14 +6269,8 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">

--- a/artfynd/A 5735-2024 artfynd.xlsx
+++ b/artfynd/A 5735-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120407540</v>
+        <v>120407505</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528288</v>
+        <v>528192</v>
       </c>
       <c r="R2" t="n">
-        <v>7180107</v>
+        <v>7180302</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,13 +782,27 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120407532</v>
+        <v>120407512</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,34 +836,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528351</v>
+        <v>528652</v>
       </c>
       <c r="R3" t="n">
-        <v>7180116</v>
+        <v>7180371</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -871,7 +898,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +908,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,8 +922,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,10 +966,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120407521</v>
+        <v>120407545</v>
       </c>
       <c r="B4" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +982,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +1009,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528245</v>
+        <v>528337</v>
       </c>
       <c r="R4" t="n">
-        <v>7180338</v>
+        <v>7180044</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,7 +1044,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,12 +1054,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på granlåga och granstubbe</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,27 +1074,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1054,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120407508</v>
+        <v>120407546</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,31 +1108,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1102,10 +1135,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528230</v>
+        <v>528428</v>
       </c>
       <c r="R5" t="n">
-        <v>7180042</v>
+        <v>7180008</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1137,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,12 +1180,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,27 +1189,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1199,10 +1213,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120407516</v>
+        <v>120407532</v>
       </c>
       <c r="B6" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,21 +1229,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1239,10 +1253,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528460</v>
+        <v>528351</v>
       </c>
       <c r="R6" t="n">
-        <v>7180155</v>
+        <v>7180116</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1274,7 +1288,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,12 +1298,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på levande gran</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1316,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120407501</v>
+        <v>120407529</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,37 +1341,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528437</v>
+        <v>528606</v>
       </c>
       <c r="R7" t="n">
-        <v>7180020</v>
+        <v>7180320</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1394,7 +1400,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1404,12 +1410,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>på granlåga</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,34 +1419,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1462,10 +1437,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120407523</v>
+        <v>120407540</v>
       </c>
       <c r="B8" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1478,21 +1453,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1505,10 +1480,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528293</v>
+        <v>528288</v>
       </c>
       <c r="R8" t="n">
-        <v>7180322</v>
+        <v>7180107</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1540,7 +1515,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1550,12 +1525,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>på mossig granlåga</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,26 +1541,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1608,7 +1558,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120407537</v>
+        <v>120407541</v>
       </c>
       <c r="B9" t="n">
         <v>78542</v>
@@ -1642,16 +1592,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528203</v>
+        <v>528291</v>
       </c>
       <c r="R9" t="n">
-        <v>7180155</v>
+        <v>7180101</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1683,7 +1636,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1693,7 +1646,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1702,8 +1655,14 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1720,7 +1679,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120407543</v>
+        <v>120407526</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1754,19 +1713,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528219</v>
+        <v>528541</v>
       </c>
       <c r="R10" t="n">
-        <v>7180072</v>
+        <v>7180241</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1798,7 +1754,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1808,7 +1764,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1817,14 +1773,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1841,10 +1791,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120407539</v>
+        <v>120407518</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1857,21 +1807,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1884,10 +1834,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528282</v>
+        <v>528380</v>
       </c>
       <c r="R11" t="n">
-        <v>7180139</v>
+        <v>7180165</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1919,7 +1869,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1929,12 +1879,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1950,6 +1900,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1967,10 +1937,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120407522</v>
+        <v>120407509</v>
       </c>
       <c r="B12" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1983,26 +1953,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2010,10 +1985,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528461</v>
+        <v>528353</v>
       </c>
       <c r="R12" t="n">
-        <v>7180049</v>
+        <v>7180029</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2045,7 +2020,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2055,12 +2030,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>på granstubbe</t>
+          <t>gamla ringhack svåra att se på bild</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2069,7 +2044,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2088,14 +2062,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2113,10 +2082,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120407503</v>
+        <v>120407539</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2129,31 +2098,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2161,10 +2125,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528357</v>
+        <v>528282</v>
       </c>
       <c r="R13" t="n">
-        <v>7180172</v>
+        <v>7180139</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2196,7 +2160,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2206,12 +2170,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>gamla ringhack</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2220,27 +2184,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2258,7 +2208,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120407512</v>
+        <v>120407522</v>
       </c>
       <c r="B14" t="n">
         <v>90576</v>
@@ -2301,10 +2251,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528652</v>
+        <v>528461</v>
       </c>
       <c r="R14" t="n">
-        <v>7180371</v>
+        <v>7180049</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2336,7 +2286,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2346,12 +2296,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2404,10 +2354,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120407534</v>
+        <v>120407504</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2420,26 +2370,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2447,10 +2402,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528126</v>
+        <v>528323</v>
       </c>
       <c r="R15" t="n">
-        <v>7180169</v>
+        <v>7180317</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2482,7 +2437,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2492,7 +2447,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2501,13 +2461,27 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2525,7 +2499,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120407545</v>
+        <v>120407537</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2559,19 +2533,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528337</v>
+        <v>528203</v>
       </c>
       <c r="R16" t="n">
-        <v>7180044</v>
+        <v>7180155</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2603,7 +2574,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2613,12 +2584,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>riklig förekomst</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2627,14 +2593,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2651,7 +2611,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120407536</v>
+        <v>120407527</v>
       </c>
       <c r="B17" t="n">
         <v>78542</v>
@@ -2685,19 +2645,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528139</v>
+        <v>528613</v>
       </c>
       <c r="R17" t="n">
-        <v>7180122</v>
+        <v>7180320</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2729,7 +2686,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2739,7 +2696,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2748,14 +2705,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2772,10 +2723,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120407504</v>
+        <v>120407516</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2788,42 +2739,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528323</v>
+        <v>528460</v>
       </c>
       <c r="R18" t="n">
-        <v>7180317</v>
+        <v>7180155</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2855,7 +2798,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2865,12 +2808,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>gamla ringhack</t>
+          <t>på levande gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2881,26 +2824,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2917,10 +2840,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120407505</v>
+        <v>120407519</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2933,42 +2856,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528192</v>
+        <v>528442</v>
       </c>
       <c r="R19" t="n">
-        <v>7180302</v>
+        <v>7180203</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -3000,7 +2915,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3010,12 +2925,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>gamla ringhack</t>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3026,26 +2941,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3062,10 +2957,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120407530</v>
+        <v>120407520</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3078,34 +2973,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528541</v>
+        <v>528255</v>
       </c>
       <c r="R20" t="n">
-        <v>7180305</v>
+        <v>7180313</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3137,7 +3035,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3147,7 +3045,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>på stående död gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3156,8 +3059,34 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3174,10 +3103,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120407541</v>
+        <v>120407502</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3190,26 +3119,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3217,10 +3151,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528291</v>
+        <v>528548</v>
       </c>
       <c r="R21" t="n">
-        <v>7180101</v>
+        <v>7180297</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3252,7 +3186,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3262,7 +3196,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3271,13 +3210,27 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3295,7 +3248,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120407529</v>
+        <v>120407530</v>
       </c>
       <c r="B22" t="n">
         <v>78542</v>
@@ -3335,10 +3288,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528606</v>
+        <v>528541</v>
       </c>
       <c r="R22" t="n">
-        <v>7180320</v>
+        <v>7180305</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3370,7 +3323,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3380,7 +3333,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3407,10 +3360,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120407527</v>
+        <v>120407511</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3423,34 +3376,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528613</v>
+        <v>528545</v>
       </c>
       <c r="R23" t="n">
-        <v>7180320</v>
+        <v>7180246</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3482,7 +3438,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3492,7 +3448,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>på levande gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3501,8 +3462,34 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3665,7 +3652,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120407544</v>
+        <v>120407543</v>
       </c>
       <c r="B25" t="n">
         <v>78542</v>
@@ -3708,10 +3695,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528244</v>
+        <v>528219</v>
       </c>
       <c r="R25" t="n">
-        <v>7180026</v>
+        <v>7180072</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3743,7 +3730,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3753,7 +3740,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3786,10 +3773,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120407531</v>
+        <v>120407515</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3802,34 +3789,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528412</v>
+        <v>528590</v>
       </c>
       <c r="R26" t="n">
-        <v>7180115</v>
+        <v>7180408</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3861,7 +3851,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3871,7 +3861,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>på stubbe av gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3880,8 +3875,34 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3898,10 +3919,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120407515</v>
+        <v>120407524</v>
       </c>
       <c r="B27" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3914,21 +3935,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3941,10 +3962,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528590</v>
+        <v>528083</v>
       </c>
       <c r="R27" t="n">
-        <v>7180408</v>
+        <v>7180143</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3976,7 +3997,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3986,12 +4007,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>på stubbe av gran</t>
+          <t>på granlåga med bark</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4021,12 +4042,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4044,10 +4065,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120407511</v>
+        <v>120407534</v>
       </c>
       <c r="B28" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4060,21 +4081,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4087,10 +4108,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528545</v>
+        <v>528126</v>
       </c>
       <c r="R28" t="n">
-        <v>7180246</v>
+        <v>7180169</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4122,7 +4143,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4132,12 +4153,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>på levande gran</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4152,27 +4168,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4190,10 +4186,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120407509</v>
+        <v>120407500</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4206,31 +4202,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4238,10 +4229,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528353</v>
+        <v>528382</v>
       </c>
       <c r="R29" t="n">
-        <v>7180029</v>
+        <v>7180168</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4273,7 +4264,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4283,12 +4274,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>gamla ringhack svåra att se på bild</t>
+          <t>på rotvälta gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4297,6 +4288,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4315,9 +4307,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4335,10 +4332,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120407525</v>
+        <v>120407501</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4351,34 +4348,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528528</v>
+        <v>528437</v>
       </c>
       <c r="R30" t="n">
-        <v>7180138</v>
+        <v>7180020</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4420,7 +4420,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4429,8 +4434,34 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4447,10 +4478,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120407506</v>
+        <v>120407544</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4463,31 +4494,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4495,10 +4521,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528073</v>
+        <v>528244</v>
       </c>
       <c r="R31" t="n">
-        <v>7180125</v>
+        <v>7180026</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4530,7 +4556,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4540,12 +4566,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4554,27 +4575,13 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4592,7 +4599,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120407526</v>
+        <v>120407536</v>
       </c>
       <c r="B32" t="n">
         <v>78542</v>
@@ -4626,16 +4633,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528541</v>
+        <v>528139</v>
       </c>
       <c r="R32" t="n">
-        <v>7180241</v>
+        <v>7180122</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4667,7 +4677,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4677,7 +4687,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4686,8 +4696,14 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4704,10 +4720,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120407502</v>
+        <v>120407517</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4720,42 +4736,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528548</v>
+        <v>528388</v>
       </c>
       <c r="R33" t="n">
-        <v>7180297</v>
+        <v>7180174</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4787,7 +4795,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4797,12 +4805,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>gamla ringhack</t>
+          <t>på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4813,26 +4821,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4849,10 +4837,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120407520</v>
+        <v>120407535</v>
       </c>
       <c r="B34" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4865,21 +4853,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4892,10 +4880,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528255</v>
+        <v>528075</v>
       </c>
       <c r="R34" t="n">
-        <v>7180313</v>
+        <v>7180118</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4927,7 +4915,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4937,12 +4925,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>på stående död gran</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4958,26 +4941,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4995,7 +4958,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120407546</v>
+        <v>120407531</v>
       </c>
       <c r="B35" t="n">
         <v>78542</v>
@@ -5029,19 +4992,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528428</v>
+        <v>528412</v>
       </c>
       <c r="R35" t="n">
-        <v>7180008</v>
+        <v>7180115</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -5073,7 +5033,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5083,7 +5043,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5092,14 +5052,8 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -5116,7 +5070,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120407528</v>
+        <v>120407547</v>
       </c>
       <c r="B36" t="n">
         <v>78542</v>
@@ -5150,16 +5104,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528642</v>
+        <v>528462</v>
       </c>
       <c r="R36" t="n">
-        <v>7180325</v>
+        <v>7180092</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5191,7 +5148,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5201,7 +5158,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5210,8 +5167,14 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5228,10 +5191,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120407535</v>
+        <v>120407523</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5244,21 +5207,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5271,10 +5234,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528075</v>
+        <v>528293</v>
       </c>
       <c r="R37" t="n">
-        <v>7180118</v>
+        <v>7180322</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5306,7 +5269,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5316,7 +5279,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>på mossig granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5332,6 +5300,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5349,10 +5337,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120407547</v>
+        <v>120407508</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5365,26 +5353,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5392,10 +5385,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528462</v>
+        <v>528230</v>
       </c>
       <c r="R38" t="n">
-        <v>7180092</v>
+        <v>7180042</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5427,7 +5420,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5437,7 +5430,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5446,13 +5444,27 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5470,10 +5482,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120407518</v>
+        <v>120407507</v>
       </c>
       <c r="B39" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5486,26 +5498,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5513,10 +5530,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528380</v>
+        <v>528230</v>
       </c>
       <c r="R39" t="n">
-        <v>7180165</v>
+        <v>7180117</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5548,7 +5565,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5558,12 +5575,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5572,7 +5589,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5591,14 +5607,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5616,10 +5627,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120407524</v>
+        <v>120407525</v>
       </c>
       <c r="B40" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5632,37 +5643,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528083</v>
+        <v>528528</v>
       </c>
       <c r="R40" t="n">
-        <v>7180143</v>
+        <v>7180138</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5694,7 +5702,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5704,12 +5712,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>på granlåga med bark</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5718,34 +5721,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5762,10 +5739,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120407519</v>
+        <v>120407503</v>
       </c>
       <c r="B41" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5778,34 +5755,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528442</v>
+        <v>528357</v>
       </c>
       <c r="R41" t="n">
-        <v>7180203</v>
+        <v>7180172</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5837,7 +5822,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5847,12 +5832,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>på granstubbe</t>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5863,6 +5848,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5879,7 +5884,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120407507</v>
+        <v>120407506</v>
       </c>
       <c r="B42" t="n">
         <v>57320</v>
@@ -5927,10 +5932,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528230</v>
+        <v>528073</v>
       </c>
       <c r="R42" t="n">
-        <v>7180117</v>
+        <v>7180125</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5962,7 +5967,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5972,7 +5977,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6024,10 +6029,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120407500</v>
+        <v>120407521</v>
       </c>
       <c r="B43" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6040,21 +6045,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6067,10 +6072,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528382</v>
+        <v>528245</v>
       </c>
       <c r="R43" t="n">
-        <v>7180168</v>
+        <v>7180338</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -6102,7 +6107,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6112,12 +6117,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>på rotvälta gran</t>
+          <t>på granlåga och granstubbe</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6170,10 +6175,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120407517</v>
+        <v>120407528</v>
       </c>
       <c r="B44" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6186,21 +6191,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6210,10 +6215,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528388</v>
+        <v>528642</v>
       </c>
       <c r="R44" t="n">
-        <v>7180174</v>
+        <v>7180325</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -6245,7 +6250,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6255,12 +6260,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>på högstubbe av gran</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 5735-2024 artfynd.xlsx
+++ b/artfynd/A 5735-2024 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120407512</v>
+        <v>120407545</v>
       </c>
       <c r="B3" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,21 +836,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528652</v>
+        <v>528337</v>
       </c>
       <c r="R3" t="n">
-        <v>7180371</v>
+        <v>7180044</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -898,7 +898,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,27 +928,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -966,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120407545</v>
+        <v>120407512</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -982,21 +962,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1009,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528337</v>
+        <v>528652</v>
       </c>
       <c r="R4" t="n">
-        <v>7180044</v>
+        <v>7180371</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1044,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,12 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1074,7 +1054,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120407526</v>
+        <v>120407518</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1695,34 +1695,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528541</v>
+        <v>528380</v>
       </c>
       <c r="R10" t="n">
-        <v>7180241</v>
+        <v>7180165</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1754,7 +1757,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1764,7 +1767,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,8 +1781,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1791,10 +1825,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120407518</v>
+        <v>120407509</v>
       </c>
       <c r="B11" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1807,26 +1841,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1834,10 +1873,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528380</v>
+        <v>528353</v>
       </c>
       <c r="R11" t="n">
-        <v>7180165</v>
+        <v>7180029</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1869,7 +1908,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1879,12 +1918,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>gamla ringhack svåra att se på bild</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,7 +1932,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1912,14 +1950,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1937,10 +1970,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120407509</v>
+        <v>120407526</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1953,42 +1986,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528353</v>
+        <v>528541</v>
       </c>
       <c r="R12" t="n">
-        <v>7180029</v>
+        <v>7180241</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2020,7 +2045,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2030,12 +2055,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>gamla ringhack svåra att se på bild</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2046,26 +2066,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -3248,10 +3248,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120407530</v>
+        <v>120407511</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3264,34 +3264,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528541</v>
+        <v>528545</v>
       </c>
       <c r="R22" t="n">
-        <v>7180305</v>
+        <v>7180246</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3323,7 +3326,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3333,7 +3336,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>på levande gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3342,8 +3350,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3360,7 +3394,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120407511</v>
+        <v>120407514</v>
       </c>
       <c r="B23" t="n">
         <v>90576</v>
@@ -3403,10 +3437,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528545</v>
+        <v>528639</v>
       </c>
       <c r="R23" t="n">
-        <v>7180246</v>
+        <v>7180387</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3438,7 +3472,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3448,12 +3482,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på levande gran</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3483,12 +3517,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3506,10 +3540,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120407514</v>
+        <v>120407530</v>
       </c>
       <c r="B24" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3522,37 +3556,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528639</v>
+        <v>528541</v>
       </c>
       <c r="R24" t="n">
-        <v>7180387</v>
+        <v>7180305</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3584,7 +3615,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3594,12 +3625,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>på död stående gran</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3608,34 +3634,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -4837,10 +4837,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120407535</v>
+        <v>120407523</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4853,21 +4853,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528075</v>
+        <v>528293</v>
       </c>
       <c r="R34" t="n">
-        <v>7180118</v>
+        <v>7180322</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4925,7 +4925,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>på mossig granlåga</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4941,6 +4946,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4958,7 +4983,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120407531</v>
+        <v>120407535</v>
       </c>
       <c r="B35" t="n">
         <v>78542</v>
@@ -4992,16 +5017,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528412</v>
+        <v>528075</v>
       </c>
       <c r="R35" t="n">
-        <v>7180115</v>
+        <v>7180118</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -5033,7 +5061,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5043,7 +5071,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5052,8 +5080,14 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -5070,7 +5104,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120407547</v>
+        <v>120407531</v>
       </c>
       <c r="B36" t="n">
         <v>78542</v>
@@ -5104,19 +5138,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528462</v>
+        <v>528412</v>
       </c>
       <c r="R36" t="n">
-        <v>7180092</v>
+        <v>7180115</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5148,7 +5179,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5158,7 +5189,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5167,14 +5198,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5191,10 +5216,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120407523</v>
+        <v>120407547</v>
       </c>
       <c r="B37" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5207,21 +5232,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5234,10 +5259,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528293</v>
+        <v>528462</v>
       </c>
       <c r="R37" t="n">
-        <v>7180322</v>
+        <v>7180092</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5269,7 +5294,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5279,12 +5304,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>på mossig granlåga</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5300,26 +5320,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -6029,10 +6029,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120407521</v>
+        <v>120407528</v>
       </c>
       <c r="B43" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6045,37 +6045,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528245</v>
+        <v>528642</v>
       </c>
       <c r="R43" t="n">
-        <v>7180338</v>
+        <v>7180325</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -6107,7 +6104,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6117,12 +6114,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>på granlåga och granstubbe</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6131,34 +6123,8 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6175,10 +6141,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120407528</v>
+        <v>120407521</v>
       </c>
       <c r="B44" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6191,34 +6157,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytterrissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528642</v>
+        <v>528245</v>
       </c>
       <c r="R44" t="n">
-        <v>7180325</v>
+        <v>7180338</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -6250,7 +6219,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6260,7 +6229,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>på granlåga och granstubbe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6269,8 +6243,34 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
